--- a/AI云业务/客户结算/星瀚云业务消耗费用.xlsx
+++ b/AI云业务/客户结算/星瀚云业务消耗费用.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿里云" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="月度汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="阿里云" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -519,32 +519,37 @@
           <t>账号信息</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>实际消耗（￥）</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>币种</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>实际消耗（原币）</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>服务费比例</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>服务费金额（￥）</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>结算总金额（￥）</t>
+          <t>服务费金额（原币）</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>结算总金额（原币）</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>服务费是否支付</t>
         </is>
@@ -566,28 +571,33 @@
           <t>星瀚</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>748.45</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>748.45</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -605,28 +615,33 @@
           <t>星瀚</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>1303.26</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>1303.26</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -644,28 +659,33 @@
           <t>星瀚</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>1466.59</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>1466.59</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -675,18 +695,18 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="n">
+      <c r="E6" s="7" t="n">
         <v>3518.3</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>3518.3</v>
       </c>
-      <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
